--- a/cet4/result/18_重生女帝_凤鸣九天/18_重生女帝_凤鸣九天_学习版.xlsx
+++ b/cet4/result/18_重生女帝_凤鸣九天/18_重生女帝_凤鸣九天_学习版.xlsx
@@ -397,787 +397,773 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D54"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>republic</v>
       </c>
       <c r="B2" t="str">
-        <v>republic</v>
+        <v>/rɪˈpʌblɪk/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>共和国</v>
       </c>
-      <c r="D2" t="str">
-        <v>republic(共和国)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>mainland</v>
       </c>
       <c r="B3" t="str">
-        <v>mainland</v>
+        <v>/ˈmeɪnlænd/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>大陆</v>
       </c>
-      <c r="D3" t="str">
-        <v>mainland(大陆)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>rebellion</v>
       </c>
       <c r="B4" t="str">
-        <v>rebellion</v>
+        <v>/rɪˈbeljən/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>叛乱</v>
       </c>
-      <c r="D4" t="str">
-        <v>rebellion(叛乱)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>debt</v>
       </c>
       <c r="B5" t="str">
-        <v>debt</v>
+        <v>/det/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>债务</v>
       </c>
-      <c r="D5" t="str">
-        <v>debt(债务)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>decay</v>
       </c>
       <c r="B6" t="str">
-        <v>decay</v>
+        <v>/dɪˈkeɪ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D6" t="str">
         <v>衰退</v>
       </c>
-      <c r="D6" t="str">
-        <v>decay(衰退)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>ten</v>
       </c>
       <c r="B7" t="str">
-        <v>ten</v>
+        <v>/ten/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./num.</v>
+      </c>
+      <c r="D7" t="str">
         <v>十</v>
       </c>
-      <c r="D7" t="str">
-        <v>ten(十)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>adjective</v>
       </c>
       <c r="B8" t="str">
-        <v>adjective</v>
+        <v>/ˈædʒɪktɪv/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>形容词</v>
       </c>
-      <c r="D8" t="str">
-        <v>adjective(形容词)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>concentrate</v>
       </c>
       <c r="B9" t="str">
-        <v>concentrate</v>
+        <v>/ˈkɑːnsntreɪt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>集中</v>
       </c>
-      <c r="D9" t="str">
-        <v>concentrate(集中)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>knowledge</v>
       </c>
       <c r="B10" t="str">
-        <v>knowledge</v>
+        <v>/ˈnɑːlɪdʒ/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>知识</v>
       </c>
-      <c r="D10" t="str">
-        <v>knowledge(知识)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>grandfather</v>
       </c>
       <c r="B11" t="str">
-        <v>grandfather</v>
+        <v>/ˈɡrænfɑːðər/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>祖父</v>
       </c>
-      <c r="D11" t="str">
-        <v>grandfather(祖父)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>naughty</v>
       </c>
       <c r="B12" t="str">
-        <v>naughty</v>
+        <v>/ˈnɔːti/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>顽皮的</v>
       </c>
-      <c r="D12" t="str">
-        <v>naughty(顽皮的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>distinguish</v>
       </c>
       <c r="B13" t="str">
-        <v>distinguish</v>
+        <v>/dɪˈstɪŋɡwɪʃ/</v>
       </c>
       <c r="C13" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>区分</v>
       </c>
-      <c r="D13" t="str">
-        <v>distinguish(区分)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>commander</v>
       </c>
       <c r="B14" t="str">
-        <v>commander</v>
+        <v>/kəˈmændər/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>指挥官</v>
       </c>
-      <c r="D14" t="str">
-        <v>commander(指挥官)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>timber</v>
       </c>
       <c r="B15" t="str">
-        <v>timber</v>
+        <v>/ˈtɪmbər/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>木材</v>
       </c>
-      <c r="D15" t="str">
-        <v>timber(木材)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>mouthful</v>
       </c>
       <c r="B16" t="str">
-        <v>mouthful</v>
+        <v>/ˈmaʊθfʊl/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>一口</v>
       </c>
-      <c r="D16" t="str">
-        <v>mouthful(一口)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>moral</v>
       </c>
       <c r="B17" t="str">
-        <v>moral</v>
+        <v>/ˈmɔːrəl/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>道德</v>
       </c>
-      <c r="D17" t="str">
-        <v>moral(道德)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>frequency</v>
       </c>
       <c r="B18" t="str">
-        <v>frequency</v>
+        <v>/ˈfriːkwənsi/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>频率</v>
       </c>
-      <c r="D18" t="str">
-        <v>frequency(频率)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>public</v>
       </c>
       <c r="B19" t="str">
-        <v>public</v>
+        <v>/ˈpʌblɪk/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>公众的</v>
       </c>
-      <c r="D19" t="str">
-        <v>public(公众的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>kneel</v>
       </c>
       <c r="B20" t="str">
-        <v>kneel</v>
+        <v>/niːl/</v>
       </c>
       <c r="C20" t="str">
+        <v>vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>跪下</v>
       </c>
-      <c r="D20" t="str">
-        <v>kneel(跪下)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>how</v>
       </c>
       <c r="B21" t="str">
-        <v>how</v>
+        <v>/haʊ/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v./adv./conj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>如何</v>
       </c>
-      <c r="D21" t="str">
-        <v>how(如何)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>unload</v>
       </c>
       <c r="B22" t="str">
-        <v>unload</v>
+        <v>/ˌʌnˈloʊd/</v>
       </c>
       <c r="C22" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>卸载</v>
       </c>
-      <c r="D22" t="str">
-        <v>unload(卸载)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>special</v>
       </c>
       <c r="B23" t="str">
-        <v>special</v>
+        <v>/ˈspeʃl/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>特殊</v>
       </c>
-      <c r="D23" t="str">
-        <v>special(特殊)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>preparation</v>
       </c>
       <c r="B24" t="str">
-        <v>preparation</v>
+        <v>/ˌprepəˈreɪʃn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>准备</v>
       </c>
-      <c r="D24" t="str">
-        <v>preparation(准备)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>below</v>
       </c>
       <c r="B25" t="str">
-        <v>below</v>
+        <v>/bɪˈloʊ/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./adv./prep.</v>
+      </c>
+      <c r="D25" t="str">
         <v>在下面</v>
       </c>
-      <c r="D25" t="str">
-        <v>below(在下面)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>roar</v>
       </c>
       <c r="B26" t="str">
-        <v>roar</v>
+        <v>/rɔːr/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D26" t="str">
         <v>咆哮</v>
       </c>
-      <c r="D26" t="str">
-        <v>roar(咆哮)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>full</v>
       </c>
       <c r="B27" t="str">
-        <v>full</v>
+        <v>/fʊl/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./v./adj./adv.</v>
+      </c>
+      <c r="D27" t="str">
         <v>完整的</v>
       </c>
-      <c r="D27" t="str">
-        <v>full(完整的)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>fearful</v>
       </c>
       <c r="B28" t="str">
-        <v>fearful</v>
+        <v>/ˈfɪrfl/</v>
       </c>
       <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>可怕的</v>
       </c>
-      <c r="D28" t="str">
-        <v>fearful(可怕的)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>reward</v>
       </c>
       <c r="B29" t="str">
-        <v>reward</v>
+        <v>/rɪˈwɔːrd/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D29" t="str">
         <v>奖励</v>
       </c>
-      <c r="D29" t="str">
-        <v>reward(奖励)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>molecule</v>
       </c>
       <c r="B30" t="str">
-        <v>molecule</v>
+        <v>/ˈmɑːlɪkjuːl/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>分子</v>
       </c>
-      <c r="D30" t="str">
-        <v>molecule(分子)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>market</v>
       </c>
       <c r="B31" t="str">
-        <v>market</v>
+        <v>/ˈmɑːrkɪt/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>市场</v>
       </c>
-      <c r="D31" t="str">
-        <v>market(市场)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>intelligent</v>
       </c>
       <c r="B32" t="str">
-        <v>intelligent</v>
+        <v>/ɪnˈtelɪdʒənt/</v>
       </c>
       <c r="C32" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>智能的</v>
       </c>
-      <c r="D32" t="str">
-        <v>intelligent(智能的)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>eleven</v>
       </c>
       <c r="B33" t="str">
-        <v>eleven</v>
+        <v>/ɪˈlevn/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D33" t="str">
         <v>十一</v>
       </c>
-      <c r="D33" t="str">
-        <v>eleven(十一)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>rice</v>
       </c>
       <c r="B34" t="str">
-        <v>rice</v>
+        <v>/raɪs/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D34" t="str">
         <v>大米</v>
       </c>
-      <c r="D34" t="str">
-        <v>rice(大米)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>banner</v>
       </c>
       <c r="B35" t="str">
-        <v>banner</v>
+        <v>/ˈbænər/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>横幅</v>
       </c>
-      <c r="D35" t="str">
-        <v>banner(横幅)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>basin</v>
       </c>
       <c r="B36" t="str">
-        <v>basin</v>
+        <v>/ˈbeɪsn/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>盆地</v>
       </c>
-      <c r="D36" t="str">
-        <v>basin(盆地)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>purely</v>
       </c>
       <c r="B37" t="str">
-        <v>purely</v>
+        <v>/ˈpjʊrli/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D37" t="str">
         <v>纯粹地</v>
       </c>
-      <c r="D37" t="str">
-        <v>purely(纯粹地)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>spur</v>
       </c>
       <c r="B38" t="str">
-        <v>spur</v>
+        <v>/spɜːr/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D38" t="str">
         <v>激励</v>
       </c>
-      <c r="D38" t="str">
-        <v>spur(激励)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>startle</v>
       </c>
       <c r="B39" t="str">
-        <v>startle</v>
+        <v>/ˈstɑːrtl/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D39" t="str">
         <v>惊吓</v>
       </c>
-      <c r="D39" t="str">
-        <v>startle(惊吓)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>trousers</v>
       </c>
       <c r="B40" t="str">
-        <v>intelligent</v>
+        <v>/ˈtraʊzərz/</v>
       </c>
       <c r="C40" t="str">
-        <v>智能的</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>intelligent(智能的)📢</v>
+        <v>裤子</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>joyful</v>
       </c>
       <c r="B41" t="str">
-        <v>trousers</v>
+        <v>/ˈdʒɔɪfl/</v>
       </c>
       <c r="C41" t="str">
-        <v>裤子</v>
+        <v>adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>trousers(裤子)📢</v>
+        <v>欢喜的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>outlook</v>
       </c>
       <c r="B42" t="str">
-        <v>joyful</v>
+        <v>/ˈaʊtlʊk/</v>
       </c>
       <c r="C42" t="str">
-        <v>欢喜的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>joyful(欢喜的)📢</v>
+        <v>展望</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>insert</v>
       </c>
       <c r="B43" t="str">
-        <v>outlook</v>
+        <v>/ɪnˈsɜːrt/</v>
       </c>
       <c r="C43" t="str">
-        <v>展望</v>
+        <v>n./v.</v>
       </c>
       <c r="D43" t="str">
-        <v>outlook(展望)📢</v>
+        <v>插入</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>silly</v>
       </c>
       <c r="B44" t="str">
-        <v>insert</v>
+        <v>/ˈsɪli/</v>
       </c>
       <c r="C44" t="str">
-        <v>插入</v>
+        <v>n./adj.</v>
       </c>
       <c r="D44" t="str">
-        <v>insert(插入)📢</v>
+        <v>愚蠢的</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>happiness</v>
       </c>
       <c r="B45" t="str">
-        <v>silly</v>
+        <v>/ˈhæpinəs/</v>
       </c>
       <c r="C45" t="str">
-        <v>愚蠢的</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>silly(愚蠢的)📢</v>
+        <v>幸福</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>possibly</v>
       </c>
       <c r="B46" t="str">
-        <v>happiness</v>
+        <v>/ˈpɑːsəbli/</v>
       </c>
       <c r="C46" t="str">
-        <v>幸福</v>
+        <v>v./adv.</v>
       </c>
       <c r="D46" t="str">
-        <v>happiness(幸福)📢</v>
+        <v>可能</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>delight</v>
       </c>
       <c r="B47" t="str">
-        <v>possibly</v>
+        <v>/dɪˈlaɪt/</v>
       </c>
       <c r="C47" t="str">
-        <v>可能</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>possibly(可能)📢</v>
+        <v>高兴</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>truly</v>
       </c>
       <c r="B48" t="str">
-        <v>delight</v>
+        <v>/ˈtruːli/</v>
       </c>
       <c r="C48" t="str">
-        <v>高兴</v>
+        <v>n./v./adv.</v>
       </c>
       <c r="D48" t="str">
-        <v>delight(高兴)📢</v>
+        <v>真实地</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>equivalent</v>
       </c>
       <c r="B49" t="str">
-        <v>truly</v>
+        <v>/ɪˈkwɪvələnt/</v>
       </c>
       <c r="C49" t="str">
-        <v>真实地</v>
+        <v>n./adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>truly(真实地)📢</v>
+        <v>相等的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>temptation</v>
       </c>
       <c r="B50" t="str">
-        <v>equivalent</v>
+        <v>/tempˈteɪʃn/</v>
       </c>
       <c r="C50" t="str">
-        <v>相等的</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>equivalent(相等的)📢</v>
+        <v>诱惑</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>restless</v>
       </c>
       <c r="B51" t="str">
-        <v>temptation</v>
+        <v>/ˈrestləs/</v>
       </c>
       <c r="C51" t="str">
-        <v>诱惑</v>
+        <v>adj.</v>
       </c>
       <c r="D51" t="str">
-        <v>temptation(诱惑)📢</v>
+        <v>焦躁不安的</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>then</v>
       </c>
       <c r="B52" t="str">
-        <v>restless</v>
+        <v>/ðen/</v>
       </c>
       <c r="C52" t="str">
-        <v>焦躁不安的</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D52" t="str">
-        <v>restless(焦躁不安的)📢</v>
+        <v>然后</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>none</v>
       </c>
       <c r="B53" t="str">
-        <v>then</v>
+        <v>/nʌn/</v>
       </c>
       <c r="C53" t="str">
-        <v>然后</v>
+        <v>n./v./adv./pron.</v>
       </c>
       <c r="D53" t="str">
-        <v>then(然后)📢</v>
+        <v>没有一个</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
+      <c r="A54" t="str">
+        <v>quiz</v>
       </c>
       <c r="B54" t="str">
-        <v>none</v>
+        <v>/kwɪz/</v>
       </c>
       <c r="C54" t="str">
-        <v>没有一个</v>
+        <v>n./vt.</v>
       </c>
       <c r="D54" t="str">
-        <v>none(没有一个)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>quiz</v>
-      </c>
-      <c r="C55" t="str">
         <v>测验</v>
-      </c>
-      <c r="D55" t="str">
-        <v>quiz(测验)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
   </ignoredErrors>
 </worksheet>
 </file>